--- a/4P_Index_Decret_2016-1804_Code_Peche_Maritime.xlsx
+++ b/4P_Index_Decret_2016-1804_Code_Peche_Maritime.xlsx
@@ -601,13 +601,9 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Art. 25: ban on drift gillnets for shrimp fishing in all Senegalese waters; Art. 35: ban on devices obstructing mesh or reducing selective action; Art. 37: Minister may require selective gear to preserve resources and the marine environment.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="n">
         <v>0.75</v>
       </c>
@@ -625,21 +621,17 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>use, disposal, marine environment</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>No dedicated budget allocation in decree; licensing fees governed separately under Law 2015-18 Art. 64. Enforcement via fisheries surveillance agents and observer programme (Ch. 6).</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3">
         <f>AVERAGE(G2,I2,K2,M2,P2)</f>
         <v/>
@@ -649,7 +641,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -698,13 +690,9 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Art. 25: ban on drift gillnets for shrimp fishing in all Senegalese waters; Art. 35: ban on devices obstructing mesh or reducing selective action; Art. 37: Minister may require selective gear to preserve resources and the marine environment.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="n">
         <v>0.75</v>
       </c>
@@ -722,21 +710,17 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>use, disposal, marine environment</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>No dedicated budget allocation in decree; licensing fees governed separately under Law 2015-18 Art. 64. Enforcement via fisheries surveillance agents and observer programme (Ch. 6).</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3">
         <f>AVERAGE(G3,I3,K3,M3,P3)</f>
         <v/>
@@ -746,7 +730,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -795,13 +779,9 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Art. 25: ban on drift gillnets for shrimp fishing in all Senegalese waters; Art. 35: ban on devices obstructing mesh or reducing selective action; Art. 37: Minister may require selective gear to preserve resources and the marine environment.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="n">
         <v>0.75</v>
       </c>
@@ -819,31 +799,27 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>use, disposal, marine environment</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>No dedicated budget allocation in decree; licensing fees governed separately under Law 2015-18 Art. 64. Enforcement via fisheries surveillance agents and observer programme (Ch. 6).</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3">
         <f>AVERAGE(G4,I4,K4,M4,P4)</f>
         <v/>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Marine environment</t>
+          <t>Environmental leakage</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -852,14 +828,14 @@
         </is>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Art. 23: Minister may supplement conservation measures by order (+0.25 authority); Art. 42: temporary zone closures possible (+0.25 monitoring). No article-specific penalty for marine litter.</t>
+          <t>Art. 23: Minister may supplement conservation measures by order (+0.25 authority). Enabling power only — no mandatory obligation or subordinate order operationalising Art. 37.</t>
         </is>
       </c>
       <c r="V4" s="3">
@@ -868,7 +844,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Marine environment and habitat protection — framework for anti-pollution/gear measures.</t>
+          <t>Enabling power ('may') for marine habitat/gear measures — not in force unless operationalised by subordinate order (Rule 12).</t>
         </is>
       </c>
     </row>
